--- a/data_set/revenue.xlsx
+++ b/data_set/revenue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FMIS\Tech-project\R20-dashboard\data_set\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA70B24-FFF4-4FBC-BADE-2F99E6971AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB6D310-CF7C-40D2-B135-AF267484FF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet 2'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet 3 '!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sheet 4'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sheet 4'!$A$1:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sheet 5'!$A$1:$C$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t xml:space="preserve">   </t>
   </si>
@@ -119,9 +119,6 @@
     <t>AVAILABLE_BUDGET</t>
   </si>
   <si>
-    <t>ACCOUNT</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -155,28 +152,38 @@
     <t>DS014</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>72</t>
+    <t>EXPENDITURE_CATEGORY</t>
+  </si>
+  <si>
+    <t>MODIFIED_LAW</t>
+  </si>
+  <si>
+    <t>Staff Charges</t>
+  </si>
+  <si>
+    <t>Operating Expenditures</t>
+  </si>
+  <si>
+    <t>Investment Expenditure</t>
+  </si>
+  <si>
+    <t>Financial Charges</t>
+  </si>
+  <si>
+    <t>Transfer Expenditure</t>
+  </si>
+  <si>
+    <t>Other Expenditure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -235,7 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -245,9 +252,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -713,7 +721,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="7">
         <f>SUM(C2:C4)</f>
@@ -732,7 +740,7 @@
         <v>36698625830177</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" ref="D5:H5" si="1">SUM(G2:G4)</f>
+        <f t="shared" ref="G5:H5" si="1">SUM(G2:G4)</f>
         <v>5178952002019</v>
       </c>
       <c r="H5" s="7">
@@ -931,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7">
         <v>2141042505040</v>
@@ -942,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="7">
         <v>254513669895</v>
@@ -953,7 +961,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7">
         <v>248502009848</v>
@@ -964,7 +972,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="7">
         <v>160380784306</v>
@@ -975,7 +983,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7">
         <v>151208916327</v>
@@ -989,82 +997,115 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40BC33DF-1EAE-4DF6-9228-D45E928C50FA}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="2" customWidth="1"/>
     <col min="3" max="3" width="19.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="D1" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
+      <c r="B2" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="C2" s="7">
-        <v>2675525351251</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
+        <v>1999012198073</v>
+      </c>
+      <c r="D2" s="7">
+        <v>2195750452018</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>38</v>
+      <c r="B3" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="C3" s="7">
-        <v>2088199357300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+        <v>3798910478175</v>
+      </c>
+      <c r="D3" s="7">
+        <v>4169451374444.2002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>39</v>
+      <c r="B4" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="C4" s="7">
-        <v>271101012313</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
+        <v>748213160596</v>
+      </c>
+      <c r="D4" s="7">
+        <v>5373375876235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>40</v>
+      <c r="B5" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C5" s="7">
-        <v>221985642471</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
+        <v>551623172986</v>
+      </c>
+      <c r="D5" s="7">
+        <v>714851000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>41</v>
+      <c r="B6" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C6" s="7">
-        <v>104728322682</v>
+        <v>11633686827512</v>
+      </c>
+      <c r="D6" s="7">
+        <v>12287169847620</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7">
+        <v>4451772018</v>
+      </c>
+      <c r="D7" s="7">
+        <v>7808350000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6" xr:uid="{40BC33DF-1EAE-4DF6-9228-D45E928C50FA}"/>
+  <autoFilter ref="A1:C5" xr:uid="{40BC33DF-1EAE-4DF6-9228-D45E928C50FA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1083,10 +1124,10 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1095,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7">
         <v>10533114763920</v>
@@ -1106,7 +1147,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="7">
         <v>7240448410164</v>
@@ -1117,7 +1158,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7">
         <v>6209986668932</v>
@@ -1128,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="7">
         <v>7842111757045</v>

--- a/data_set/revenue.xlsx
+++ b/data_set/revenue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FMIS\Tech-project\R20-dashboard\data_set\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB6D310-CF7C-40D2-B135-AF267484FF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564D0B89-BDA2-4BFC-AB46-011F7E201B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,11 @@
     <sheet name="Sheet 5" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet 2'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet 2'!$A$1:$C$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet 3 '!$A$1:$C$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sheet 4'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sheet 5'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sheet 4'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sheet 5'!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t xml:space="preserve">   </t>
   </si>
@@ -62,9 +62,6 @@
     <t>CURRENT_BUDGET</t>
   </si>
   <si>
-    <t>APE</t>
-  </si>
-  <si>
     <t>National</t>
   </si>
   <si>
@@ -89,33 +86,6 @@
     <t>Mar</t>
   </si>
   <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Jul</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
-  <si>
     <t>AVAILABLE_BUDGET</t>
   </si>
   <si>
@@ -128,52 +98,34 @@
     <t>Q1</t>
   </si>
   <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>Q4</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
-    <t>PT018</t>
-  </si>
-  <si>
-    <t>PV012</t>
-  </si>
-  <si>
-    <t>PT006</t>
-  </si>
-  <si>
-    <t>DS014</t>
-  </si>
-  <si>
     <t>EXPENDITURE_CATEGORY</t>
   </si>
   <si>
     <t>MODIFIED_LAW</t>
   </si>
   <si>
-    <t>Staff Charges</t>
-  </si>
-  <si>
-    <t>Operating Expenditures</t>
-  </si>
-  <si>
-    <t>Investment Expenditure</t>
-  </si>
-  <si>
-    <t>Financial Charges</t>
-  </si>
-  <si>
-    <t>Transfer Expenditure</t>
-  </si>
-  <si>
-    <t>Other Expenditure</t>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Non-Tax</t>
+  </si>
+  <si>
+    <t>Customs</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>28000</t>
   </si>
 </sst>
 </file>
@@ -242,7 +194,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -255,7 +207,13 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -595,16 +553,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.125" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" style="7" customWidth="1"/>
-    <col min="4" max="4" width="23.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="7" customWidth="1"/>
-    <col min="7" max="7" width="20.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" style="14" customWidth="1"/>
+    <col min="4" max="4" width="23.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="14" customWidth="1"/>
+    <col min="7" max="7" width="20.875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9.125" style="7"/>
   </cols>
@@ -616,147 +574,140 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7">
-        <v>161473900000</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="C2" s="14">
+        <v>29814035000000</v>
+      </c>
+      <c r="D2" s="15">
         <v>0</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="15">
         <v>0</v>
       </c>
-      <c r="F2" s="7">
-        <v>161473900000</v>
+      <c r="F2" s="15">
+        <v>29814035000000</v>
       </c>
       <c r="G2" s="7">
-        <v>-3737997981</v>
+        <v>2800114929286</v>
       </c>
       <c r="H2" s="7">
-        <f>F2-G2</f>
-        <v>165211897981</v>
+        <f t="shared" ref="H2" si="0">F2-G2</f>
+        <v>27013920070714</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7">
-        <v>28320545000000</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="C3" s="14">
+        <v>6552043275696</v>
+      </c>
+      <c r="D3" s="15">
+        <v>-5020900438</v>
+      </c>
+      <c r="E3" s="15">
         <v>0</v>
       </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>28320545000000</v>
+      <c r="F3" s="15">
+        <v>6557064176134</v>
       </c>
       <c r="G3" s="7">
-        <v>2235500000000</v>
+        <v>4371170343501</v>
       </c>
       <c r="H3" s="7">
-        <f t="shared" ref="H3" si="0">F3-G3</f>
-        <v>26085045000000</v>
+        <f>F3-G3</f>
+        <v>2185893832633</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7">
-        <v>8118598606972</v>
-      </c>
-      <c r="D4" s="7">
-        <v>98008323205</v>
-      </c>
-      <c r="E4" s="7">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="14">
+        <f>SUM(C2:C3)</f>
+        <v>36366078275696</v>
+      </c>
+      <c r="D4" s="14">
+        <f>SUM(D2:D3)</f>
+        <v>-5020900438</v>
+      </c>
+      <c r="E4" s="14">
+        <f>SUM(E2:E3)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="7">
-        <v>8216606930177</v>
+      <c r="F4" s="14">
+        <f>SUM(F2:F3)</f>
+        <v>36371099176134</v>
       </c>
       <c r="G4" s="7">
-        <v>2947190000000</v>
+        <f>SUM(G2:G3)</f>
+        <v>7171285272787</v>
       </c>
       <c r="H4" s="7">
-        <f>F4-G4</f>
-        <v>5269416930177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>5</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="7">
-        <f>SUM(C2:C4)</f>
-        <v>36600617506972</v>
-      </c>
-      <c r="D5" s="7">
-        <f>SUM(D2:D4)</f>
-        <v>98008323205</v>
-      </c>
-      <c r="E5" s="7">
-        <f>SUM(E2:E4)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <f>SUM(F2:F4)</f>
-        <v>36698625830177</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" ref="G5:H5" si="1">SUM(G2:G4)</f>
-        <v>5178952002019</v>
-      </c>
-      <c r="H5" s="7">
-        <f t="shared" si="1"/>
-        <v>31519673828158</v>
-      </c>
+        <f>SUM(H2:H3)</f>
+        <v>29199813903347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4778C0B-F336-46B9-A589-71D74EC00AB3}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
@@ -769,146 +720,47 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
+      <c r="B2" s="18" t="s">
+        <v>11</v>
       </c>
       <c r="C2" s="7">
-        <v>2417206062896</v>
+        <v>2900058691514</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
+      <c r="B3" s="18" t="s">
+        <v>12</v>
       </c>
       <c r="C3" s="7">
-        <v>5094467965508</v>
+        <v>3896540165083</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
+      <c r="B4" s="18" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="7">
-        <v>3021440735516</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7">
-        <v>2450767685158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7">
-        <v>2161442275097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7">
-        <v>2628238449909</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2636551148524</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1760127443335</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1813308077073</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2770812747197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="7">
-        <v>2143092411154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2928206598694</v>
+        <v>374686416190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13" xr:uid="{D4778C0B-F336-46B9-A589-71D74EC00AB3}"/>
+  <autoFilter ref="A1:C4" xr:uid="{D4778C0B-F336-46B9-A589-71D74EC00AB3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -928,65 +780,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
+      <c r="B2" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="C2" s="7">
-        <v>2141042505040</v>
+        <v>2453356336199</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>32</v>
+      <c r="B3" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="C3" s="7">
-        <v>254513669895</v>
+        <v>243874700199</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
+      <c r="B4" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="C4" s="7">
-        <v>248502009848</v>
+        <v>16376565890</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
+      <c r="B5" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="7">
-        <v>160380784306</v>
+        <v>14989681500</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="C6" s="7">
-        <v>151208916327</v>
+        <v>2457494375</v>
       </c>
     </row>
   </sheetData>
@@ -997,13 +849,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40BC33DF-1EAE-4DF6-9228-D45E928C50FA}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1011,108 +863,66 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>38</v>
+      <c r="B2" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="C2" s="7">
-        <v>1999012198073</v>
+        <v>1810017364573</v>
       </c>
       <c r="D2" s="7">
-        <v>2195750452018</v>
+        <v>43243196000000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>39</v>
+      <c r="B3" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="C3" s="7">
-        <v>3798910478175</v>
+        <v>3653284029626</v>
       </c>
       <c r="D3" s="7">
-        <v>4169451374444.2002</v>
+        <v>12926521113900</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>40</v>
+      <c r="B4" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C4" s="7">
-        <v>748213160596</v>
+        <v>1627310935279</v>
       </c>
       <c r="D4" s="7">
-        <v>5373375876235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="7">
-        <v>551623172986</v>
-      </c>
-      <c r="D5" s="7">
-        <v>714851000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="7">
-        <v>11633686827512</v>
-      </c>
-      <c r="D6" s="7">
-        <v>12287169847620</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="7">
-        <v>4451772018</v>
-      </c>
-      <c r="D7" s="7">
-        <v>7808350000</v>
+        <v>33759400000000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C5" xr:uid="{40BC33DF-1EAE-4DF6-9228-D45E928C50FA}"/>
+  <autoFilter ref="A1:C4" xr:uid="{40BC33DF-1EAE-4DF6-9228-D45E928C50FA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C422C38-199D-42CF-BC1B-FCE487D9B7BD}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
@@ -1125,10 +935,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1136,47 +946,14 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C2" s="7">
-        <v>10533114763920</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="7">
-        <v>7240448410164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="7">
-        <v>6209986668932</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="7">
-        <v>7842111757045</v>
+        <v>7171285272787</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C5" xr:uid="{3C422C38-199D-42CF-BC1B-FCE487D9B7BD}"/>
+  <autoFilter ref="A1:C2" xr:uid="{3C422C38-199D-42CF-BC1B-FCE487D9B7BD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_set/revenue.xlsx
+++ b/data_set/revenue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FMIS\Tech-project\R20-dashboard\data_set\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564D0B89-BDA2-4BFC-AB46-011F7E201B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBBA390-0498-461A-912F-10D9BA482CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Sheet 3 " sheetId="4" r:id="rId3"/>
     <sheet name="Sheet 4" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet 5" sheetId="6" r:id="rId5"/>
+    <sheet name="M_2025" sheetId="7" r:id="rId6"/>
+    <sheet name="Q_2025" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$5</definedName>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t xml:space="preserve">   </t>
   </si>
@@ -126,6 +128,42 @@
   </si>
   <si>
     <t>28000</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q4</t>
   </si>
 </sst>
 </file>
@@ -194,7 +232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -207,13 +245,15 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -558,10 +598,10 @@
   <cols>
     <col min="1" max="1" width="4.125" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" style="14" customWidth="1"/>
-    <col min="4" max="4" width="23.75" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.625" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="14" customWidth="1"/>
+    <col min="3" max="3" width="25" style="13" customWidth="1"/>
+    <col min="4" max="4" width="23.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="13" customWidth="1"/>
     <col min="7" max="7" width="20.875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9.125" style="7"/>
@@ -574,16 +614,16 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -597,19 +637,19 @@
       <c r="A2" s="7">
         <v>3</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>29814035000000</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="14">
         <v>29814035000000</v>
       </c>
       <c r="G2" s="7">
@@ -624,19 +664,19 @@
       <c r="A3" s="7">
         <v>4</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>6552043275696</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="14">
         <v>-5020900438</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="14">
         <v>0</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>6557064176134</v>
       </c>
       <c r="G3" s="7">
@@ -654,50 +694,50 @@
       <c r="B4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="14">
-        <f>SUM(C2:C3)</f>
+      <c r="C4" s="13">
+        <f t="shared" ref="C4:H4" si="1">SUM(C2:C3)</f>
         <v>36366078275696</v>
       </c>
-      <c r="D4" s="14">
-        <f>SUM(D2:D3)</f>
+      <c r="D4" s="13">
+        <f t="shared" si="1"/>
         <v>-5020900438</v>
       </c>
-      <c r="E4" s="14">
-        <f>SUM(E2:E3)</f>
+      <c r="E4" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F4" s="14">
-        <f>SUM(F2:F3)</f>
+      <c r="F4" s="13">
+        <f t="shared" si="1"/>
         <v>36371099176134</v>
       </c>
       <c r="G4" s="7">
-        <f>SUM(G2:G3)</f>
+        <f t="shared" si="1"/>
         <v>7171285272787</v>
       </c>
       <c r="H4" s="7">
-        <f>SUM(H2:H3)</f>
+        <f t="shared" si="1"/>
         <v>29199813903347</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="G10"/>
+      <c r="H10"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="G11"/>
+      <c r="H11"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -730,7 +770,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="7">
@@ -741,7 +781,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="7">
@@ -752,7 +792,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="7">
@@ -790,7 +830,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="7">
@@ -801,7 +841,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="7">
@@ -812,7 +852,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" s="7">
@@ -823,7 +863,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="7">
@@ -834,7 +874,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="7">
@@ -956,4 +996,232 @@
   <autoFilter ref="A1:C2" xr:uid="{3C422C38-199D-42CF-BC1B-FCE487D9B7BD}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B16093-C250-4431-BDBA-13C833086BB7}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="17">
+        <v>2441819538066</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="17">
+        <v>5291282994515</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="17">
+        <v>3805196719389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="17">
+        <v>2781714893822</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="17">
+        <v>2698093404225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="17">
+        <v>2837854971671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="17">
+        <v>2979524677398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="17">
+        <v>2455009190988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="17">
+        <v>2332591203738</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="17">
+        <v>2802051577887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="17">
+        <v>2708569569598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="17">
+        <v>3613331540310</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B03354A2-D96A-400A-A641-E40971FE926B}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.25" style="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17">
+        <v>11538299251970</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="17">
+        <v>8317663269718</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="17">
+        <v>7767125072124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="17">
+        <v>9123952687795</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>